--- a/recruiters.xlsx
+++ b/recruiters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\email_scr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6EB101E-246E-4AAB-BD9B-C4484D50CDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728F8D7E-C719-4A44-B870-3660840450C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DFF69AAB-9910-4C0F-827A-27677DF0EEA1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>email</t>
   </si>
@@ -40,6 +40,9 @@
   </si>
   <si>
     <t>linkedin</t>
+  </si>
+  <si>
+    <t>location</t>
   </si>
 </sst>
 </file>
@@ -402,15 +405,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3090AFE3-3612-4631-92B4-7D60BA0536C6}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.08984375" customWidth="1"/>
-    <col min="2" max="2" width="30.54296875" customWidth="1"/>
-    <col min="3" max="3" width="20.81640625" customWidth="1"/>
+    <col min="1" max="1" width="20.90625" customWidth="1"/>
+    <col min="2" max="2" width="14.54296875" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -426,8 +429,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
     </row>
   </sheetData>
